--- a/business_forms/036_refund_reasons_for_social_contributions--business_forms.xlsx
+++ b/business_forms/036_refund_reasons_for_social_contributions--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'contribution_reason',_'label':_'reason',_'type':_'text',_'options':_[]}</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'contribution_reason', 'label': 'Reason', 'type': 'text', 'options': []}</t>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contribution_date',_'label':_'date',_'type':_'date',_'options':_[]}</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'contribution_date', 'label': 'Date', 'type': 'date', 'options': []}</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'reason_1',_'label':_'reason_1',_'type':_'text',_'options':_[]}</t>
+          <t>reason_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'reason_1', 'label': 'Reason 1', 'type': 'text', 'options': []}</t>
+          <t>Reason 1</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reason_2',_'label':_'reason_2',_'type':_'text',_'options':_[]}</t>
+          <t>reason_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'reason_2', 'label': 'Reason 2', 'type': 'text', 'options': []}</t>
+          <t>Reason 2</t>
         </is>
       </c>
     </row>
